--- a/dados.xlsx
+++ b/dados.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\boxplot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m7528839\OneDrive - CAMG\Área de Trabalho\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,11 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$O$1233</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -221,7 +216,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,27 +280,33 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -58819,7 +58830,58 @@
   <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="4" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="34" max="38" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="43" max="44" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="55" max="57" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="71" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:70" ht="75" x14ac:dyDescent="0.25">
@@ -59247,2496 +59309,3236 @@
       </c>
     </row>
     <row r="3" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="7">
         <v>2161.04</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="7">
         <v>206.97</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="7">
         <v>8944.0300000000007</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="7">
         <v>2593.25</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="7">
         <v>278.52</v>
       </c>
-      <c r="G3" s="3">
+      <c r="F3" s="8">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
         <v>3000.17</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="7">
         <v>192.86</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="7">
         <v>259.70999999999998</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="7">
         <v>42.92</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="7">
         <v>499.45</v>
       </c>
-      <c r="M3" s="3">
+      <c r="L3" s="8">
+        <v>0</v>
+      </c>
+      <c r="M3" s="7">
         <v>541.62</v>
       </c>
-      <c r="O3" s="3">
+      <c r="N3" s="8">
+        <v>0</v>
+      </c>
+      <c r="O3" s="7">
         <v>295.25</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="7">
         <v>217.79</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="7">
         <v>207.92</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="7">
         <v>61.28</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="7">
         <v>928.68</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3" s="7">
         <v>60.71</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3" s="7">
         <v>408.15</v>
       </c>
-      <c r="W3" s="3">
+      <c r="V3" s="8">
+        <v>0</v>
+      </c>
+      <c r="W3" s="7">
         <v>133.88999999999999</v>
       </c>
-      <c r="X3" s="3">
+      <c r="X3" s="7">
         <v>83.67</v>
       </c>
-      <c r="AA3" s="3">
+      <c r="Y3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="7">
         <v>185.7</v>
       </c>
-      <c r="AC3" s="3">
+      <c r="AB3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="7">
         <v>806.4</v>
       </c>
-      <c r="AD3" s="3">
+      <c r="AD3" s="7">
         <v>1305.1600000000001</v>
       </c>
-      <c r="AE3" s="3">
+      <c r="AE3" s="7">
         <v>410.34</v>
       </c>
-      <c r="AF3" s="3">
+      <c r="AF3" s="7">
         <v>54.4</v>
       </c>
-      <c r="AG3" s="3">
+      <c r="AG3" s="7">
         <v>1833.54</v>
       </c>
-      <c r="AH3" s="3">
+      <c r="AH3" s="7">
         <v>282.31</v>
       </c>
-      <c r="AI3" s="3">
+      <c r="AI3" s="7">
         <v>258.94</v>
       </c>
-      <c r="AJ3" s="3">
+      <c r="AJ3" s="7">
         <v>103.5</v>
       </c>
-      <c r="AK3" s="3">
+      <c r="AK3" s="7">
         <v>125.44</v>
       </c>
-      <c r="AL3" s="3">
+      <c r="AL3" s="7">
         <v>94.56</v>
       </c>
-      <c r="AM3" s="3">
+      <c r="AM3" s="7">
         <v>544.47</v>
       </c>
-      <c r="AO3" s="3">
+      <c r="AN3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="7">
         <v>119.26</v>
       </c>
-      <c r="AQ3" s="3">
+      <c r="AP3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="7">
         <v>457.82</v>
       </c>
-      <c r="AR3" s="3">
+      <c r="AR3" s="7">
         <v>395.5</v>
       </c>
-      <c r="AS3" s="3">
+      <c r="AS3" s="7">
         <v>639.37</v>
       </c>
-      <c r="AT3" s="3">
+      <c r="AT3" s="7">
         <v>109.31</v>
       </c>
-      <c r="AU3" s="3">
+      <c r="AU3" s="7">
         <v>1895.03</v>
       </c>
-      <c r="AV3" s="3">
+      <c r="AV3" s="7">
         <v>3369.23</v>
       </c>
-      <c r="AW3" s="3">
+      <c r="AW3" s="7">
         <v>40.96</v>
       </c>
-      <c r="AY3" s="3">
+      <c r="AX3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="7">
         <v>3999.98</v>
       </c>
-      <c r="AZ3" s="3">
+      <c r="AZ3" s="7">
         <v>480.47</v>
       </c>
-      <c r="BA3" s="3">
+      <c r="BA3" s="7">
         <v>6210.95</v>
       </c>
-      <c r="BB3" s="3">
+      <c r="BB3" s="7">
         <v>361.88</v>
       </c>
-      <c r="BC3" s="3">
+      <c r="BC3" s="7">
         <v>6516.64</v>
       </c>
-      <c r="BD3" s="3">
+      <c r="BD3" s="7">
         <v>420.54</v>
       </c>
-      <c r="BE3" s="3">
+      <c r="BE3" s="7">
         <v>6626.31</v>
       </c>
-      <c r="BF3" s="3">
+      <c r="BF3" s="7">
         <v>454.02</v>
       </c>
-      <c r="BG3" s="3">
+      <c r="BG3" s="7">
         <v>1567.67</v>
       </c>
-      <c r="BI3" s="3">
+      <c r="BH3" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI3" s="7">
         <v>4296.5200000000004</v>
       </c>
-      <c r="BJ3" s="3">
+      <c r="BJ3" s="7">
         <v>251.75</v>
       </c>
-      <c r="BK3" s="3">
+      <c r="BK3" s="7">
         <v>4429.1400000000003</v>
       </c>
-      <c r="BL3" s="3">
+      <c r="BL3" s="7">
         <v>583.57000000000005</v>
       </c>
-      <c r="BM3" s="3">
+      <c r="BM3" s="7">
         <v>5834.1</v>
       </c>
-      <c r="BO3" s="3">
+      <c r="BN3" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO3" s="7">
         <v>6020.33</v>
       </c>
-      <c r="BP3" s="3">
+      <c r="BP3" s="7">
         <v>382.49</v>
       </c>
-      <c r="BQ3" s="3">
+      <c r="BQ3" s="7">
         <v>4474.13</v>
       </c>
-      <c r="BR3" s="3">
+      <c r="BR3" s="7">
         <v>273.02</v>
       </c>
     </row>
     <row r="4" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="7">
         <v>2225.38</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="7">
         <v>454.19</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="7">
         <v>5152.76</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="7">
         <v>2890.16</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="7">
         <v>196.56</v>
       </c>
-      <c r="G4" s="3">
+      <c r="F4" s="8">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
         <v>3398.18</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="7">
         <v>232.04</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="7">
         <v>286.19</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="7">
         <v>50.73</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="7">
         <v>1285.8599999999999</v>
       </c>
-      <c r="M4" s="3">
+      <c r="L4" s="8">
+        <v>0</v>
+      </c>
+      <c r="M4" s="7">
         <v>636.28</v>
       </c>
-      <c r="O4" s="3">
+      <c r="N4" s="8">
+        <v>0</v>
+      </c>
+      <c r="O4" s="7">
         <v>299.10000000000002</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="7">
         <v>114.78</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="7">
         <v>432.88</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="7">
         <v>92.93</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="7">
         <v>1005.18</v>
       </c>
-      <c r="T4" s="3">
+      <c r="T4" s="7">
         <v>56.76</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U4" s="7">
         <v>423.76</v>
       </c>
-      <c r="W4" s="3">
+      <c r="V4" s="8">
+        <v>0</v>
+      </c>
+      <c r="W4" s="7">
         <v>245.04</v>
       </c>
-      <c r="X4" s="3">
+      <c r="X4" s="7">
         <v>84.86</v>
       </c>
-      <c r="AA4" s="3">
+      <c r="Y4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="7">
         <v>344.69</v>
       </c>
-      <c r="AC4" s="3">
+      <c r="AB4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="7">
         <v>616.22</v>
       </c>
-      <c r="AD4" s="3">
+      <c r="AD4" s="7">
         <v>3411.87</v>
       </c>
-      <c r="AE4" s="3">
+      <c r="AE4" s="7">
         <v>460.13</v>
       </c>
-      <c r="AF4" s="3">
+      <c r="AF4" s="7">
         <v>54.4</v>
       </c>
-      <c r="AG4" s="3">
+      <c r="AG4" s="7">
         <v>1980.64</v>
       </c>
-      <c r="AH4" s="3">
+      <c r="AH4" s="7">
         <v>237.08</v>
       </c>
-      <c r="AI4" s="3">
+      <c r="AI4" s="7">
         <v>267.55</v>
       </c>
-      <c r="AJ4" s="3">
+      <c r="AJ4" s="7">
         <v>103.37</v>
       </c>
-      <c r="AK4" s="3">
+      <c r="AK4" s="7">
         <v>180.91</v>
       </c>
-      <c r="AL4" s="3">
+      <c r="AL4" s="7">
         <v>100.73</v>
       </c>
-      <c r="AM4" s="3">
+      <c r="AM4" s="7">
         <v>747.27</v>
       </c>
-      <c r="AO4" s="3">
+      <c r="AN4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="7">
         <v>40.29</v>
       </c>
-      <c r="AQ4" s="3">
+      <c r="AP4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="7">
         <v>422.02</v>
       </c>
-      <c r="AR4" s="3">
+      <c r="AR4" s="7">
         <v>316.88</v>
       </c>
-      <c r="AS4" s="3">
+      <c r="AS4" s="7">
         <v>1288.73</v>
       </c>
-      <c r="AT4" s="3">
+      <c r="AT4" s="7">
         <v>109.31</v>
       </c>
-      <c r="AU4" s="3">
+      <c r="AU4" s="7">
         <v>1841.96</v>
       </c>
-      <c r="AV4" s="3">
+      <c r="AV4" s="7">
         <v>6896.44</v>
       </c>
-      <c r="AW4" s="3">
+      <c r="AW4" s="7">
         <v>58.19</v>
       </c>
-      <c r="AY4" s="3">
+      <c r="AX4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="7">
         <v>3920.96</v>
       </c>
-      <c r="AZ4" s="3">
+      <c r="AZ4" s="7">
         <v>476.01</v>
       </c>
-      <c r="BA4" s="3">
+      <c r="BA4" s="7">
         <v>7898.77</v>
       </c>
-      <c r="BB4" s="3">
+      <c r="BB4" s="7">
         <v>455.79</v>
       </c>
-      <c r="BC4" s="3">
+      <c r="BC4" s="7">
         <v>8935.73</v>
       </c>
-      <c r="BD4" s="3">
+      <c r="BD4" s="7">
         <v>518.42999999999995</v>
       </c>
-      <c r="BE4" s="3">
+      <c r="BE4" s="7">
         <v>7347.52</v>
       </c>
-      <c r="BF4" s="3">
+      <c r="BF4" s="7">
         <v>454.21</v>
       </c>
-      <c r="BG4" s="3">
+      <c r="BG4" s="7">
         <v>1565.92</v>
       </c>
-      <c r="BI4" s="3">
+      <c r="BH4" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI4" s="7">
         <v>6662.6</v>
       </c>
-      <c r="BJ4" s="3">
+      <c r="BJ4" s="7">
         <v>404.64</v>
       </c>
-      <c r="BK4" s="3">
+      <c r="BK4" s="7">
         <v>3949.47</v>
       </c>
-      <c r="BL4" s="3">
+      <c r="BL4" s="7">
         <v>494.95</v>
       </c>
-      <c r="BM4" s="3">
+      <c r="BM4" s="7">
         <v>5374.54</v>
       </c>
-      <c r="BO4" s="3">
+      <c r="BN4" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO4" s="7">
         <v>6695.78</v>
       </c>
-      <c r="BP4" s="3">
+      <c r="BP4" s="7">
         <v>382.49</v>
       </c>
-      <c r="BQ4" s="3">
+      <c r="BQ4" s="7">
         <v>5170.83</v>
       </c>
-      <c r="BR4" s="3">
+      <c r="BR4" s="7">
         <v>248.15</v>
       </c>
     </row>
     <row r="5" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="A5" s="7">
         <v>2054.21</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="7">
         <v>961.16</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="7">
         <v>8369.02</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="7">
         <v>2537.2800000000002</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="7">
         <v>183.5</v>
       </c>
-      <c r="G5" s="3">
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
         <v>3016.22</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="7">
         <v>231.31</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="7">
         <v>291.8</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="7">
         <v>56.78</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="7">
         <v>596.95000000000005</v>
       </c>
-      <c r="M5" s="3">
+      <c r="L5" s="8">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
         <v>663.1</v>
       </c>
-      <c r="O5" s="3">
+      <c r="N5" s="8">
+        <v>0</v>
+      </c>
+      <c r="O5" s="7">
         <v>311.75</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="7">
         <v>168.47</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="7">
         <v>426.52</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="7">
         <v>93.08</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="7">
         <v>1362.31</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="7">
         <v>79.88</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="7">
         <v>454.54</v>
       </c>
-      <c r="W5" s="3">
+      <c r="V5" s="8">
+        <v>0</v>
+      </c>
+      <c r="W5" s="7">
         <v>222.14</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="7">
         <v>103.52</v>
       </c>
-      <c r="AA5" s="3">
+      <c r="Y5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="7">
         <v>90.09</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AB5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="7">
         <v>777.66</v>
       </c>
-      <c r="AD5" s="3">
+      <c r="AD5" s="7">
         <v>535.92999999999995</v>
       </c>
-      <c r="AE5" s="3">
+      <c r="AE5" s="7">
         <v>395.38</v>
       </c>
-      <c r="AF5" s="3">
+      <c r="AF5" s="7">
         <v>54.4</v>
       </c>
-      <c r="AG5" s="3">
+      <c r="AG5" s="7">
         <v>1864.2</v>
       </c>
-      <c r="AH5" s="3">
+      <c r="AH5" s="7">
         <v>327.52999999999997</v>
       </c>
-      <c r="AI5" s="3">
+      <c r="AI5" s="7">
         <v>262.12</v>
       </c>
-      <c r="AJ5" s="3">
+      <c r="AJ5" s="7">
         <v>103.35</v>
       </c>
-      <c r="AK5" s="3">
+      <c r="AK5" s="7">
         <v>189.14</v>
       </c>
-      <c r="AL5" s="3">
+      <c r="AL5" s="7">
         <v>100.73</v>
       </c>
-      <c r="AM5" s="3">
+      <c r="AM5" s="7">
         <v>270.73</v>
       </c>
-      <c r="AO5" s="3">
+      <c r="AN5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="7">
         <v>80.58</v>
       </c>
-      <c r="AQ5" s="3">
+      <c r="AP5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="7">
         <v>504.96</v>
       </c>
-      <c r="AR5" s="3">
+      <c r="AR5" s="7">
         <v>385.67</v>
       </c>
-      <c r="AS5" s="3">
+      <c r="AS5" s="7">
         <v>1499.16</v>
       </c>
-      <c r="AT5" s="3">
+      <c r="AT5" s="7">
         <v>109.31</v>
       </c>
-      <c r="AU5" s="3">
+      <c r="AU5" s="7">
         <v>1936.34</v>
       </c>
-      <c r="AV5" s="3">
+      <c r="AV5" s="7">
         <v>18.52</v>
       </c>
-      <c r="AW5" s="3">
+      <c r="AW5" s="7">
         <v>40.96</v>
       </c>
-      <c r="AY5" s="3">
+      <c r="AX5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="7">
         <v>3206.4</v>
       </c>
-      <c r="AZ5" s="3">
+      <c r="AZ5" s="7">
         <v>494</v>
       </c>
-      <c r="BA5" s="3">
+      <c r="BA5" s="7">
         <v>7452.68</v>
       </c>
-      <c r="BB5" s="3">
+      <c r="BB5" s="7">
         <v>515.58000000000004</v>
       </c>
-      <c r="BC5" s="3">
+      <c r="BC5" s="7">
         <v>9285.4599999999991</v>
       </c>
-      <c r="BD5" s="3">
+      <c r="BD5" s="7">
         <v>495.42</v>
       </c>
-      <c r="BE5" s="3">
+      <c r="BE5" s="7">
         <v>9355.99</v>
       </c>
-      <c r="BF5" s="3">
+      <c r="BF5" s="7">
         <v>405.81</v>
       </c>
-      <c r="BG5" s="3">
+      <c r="BG5" s="7">
         <v>1706.45</v>
       </c>
-      <c r="BI5" s="3">
+      <c r="BH5" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI5" s="7">
         <v>5956.63</v>
       </c>
-      <c r="BJ5" s="3">
+      <c r="BJ5" s="7">
         <v>736.84</v>
       </c>
-      <c r="BK5" s="3">
+      <c r="BK5" s="7">
         <v>4980.9799999999996</v>
       </c>
-      <c r="BL5" s="3">
+      <c r="BL5" s="7">
         <v>676.35</v>
       </c>
-      <c r="BM5" s="3">
+      <c r="BM5" s="7">
         <v>5865.91</v>
       </c>
-      <c r="BO5" s="3">
+      <c r="BN5" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO5" s="7">
         <v>6695.78</v>
       </c>
-      <c r="BP5" s="3">
+      <c r="BP5" s="7">
         <v>397.52</v>
       </c>
-      <c r="BQ5" s="3">
+      <c r="BQ5" s="7">
         <v>5382.89</v>
       </c>
-      <c r="BR5" s="3">
+      <c r="BR5" s="7">
         <v>177.37</v>
       </c>
     </row>
     <row r="6" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="7">
         <v>1916.23</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="7">
         <v>1207.46</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="7">
         <v>4755.92</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="7">
         <v>2826.87</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="7">
         <v>181.17</v>
       </c>
-      <c r="G6" s="3">
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
         <v>2951.31</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="7">
         <v>247.97</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="7">
         <v>221.82</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="7">
         <v>43.76</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="7">
         <v>1231.8</v>
       </c>
-      <c r="M6" s="3">
+      <c r="L6" s="8">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7">
         <v>654.04999999999995</v>
       </c>
-      <c r="O6" s="3">
+      <c r="N6" s="8">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7">
         <v>297.60000000000002</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="7">
         <v>115.62</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="7">
         <v>332.61</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="7">
         <v>102.44</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="7">
         <v>1351.52</v>
       </c>
-      <c r="T6" s="3">
+      <c r="T6" s="7">
         <v>96.13</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U6" s="7">
         <v>421.91</v>
       </c>
-      <c r="W6" s="3">
+      <c r="V6" s="8">
+        <v>0</v>
+      </c>
+      <c r="W6" s="7">
         <v>209.58</v>
       </c>
-      <c r="X6" s="3">
+      <c r="X6" s="7">
         <v>91.45</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="Y6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="7">
         <v>301.83</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AB6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="7">
         <v>967.63</v>
       </c>
-      <c r="AD6" s="3">
+      <c r="AD6" s="7">
         <v>409.1</v>
       </c>
-      <c r="AE6" s="3">
+      <c r="AE6" s="7">
         <v>384.91</v>
       </c>
-      <c r="AF6" s="3">
+      <c r="AF6" s="7">
         <v>54.4</v>
       </c>
-      <c r="AG6" s="3">
+      <c r="AG6" s="7">
         <v>1959.37</v>
       </c>
-      <c r="AH6" s="3">
+      <c r="AH6" s="7">
         <v>267.27</v>
       </c>
-      <c r="AI6" s="3">
+      <c r="AI6" s="7">
         <v>244.47</v>
       </c>
-      <c r="AJ6" s="3">
+      <c r="AJ6" s="7">
         <v>103.31</v>
       </c>
-      <c r="AK6" s="3">
+      <c r="AK6" s="7">
         <v>165.41</v>
       </c>
-      <c r="AL6" s="3">
+      <c r="AL6" s="7">
         <v>100.73</v>
       </c>
-      <c r="AM6" s="3">
+      <c r="AM6" s="7">
         <v>626.70000000000005</v>
       </c>
-      <c r="AO6" s="3">
+      <c r="AN6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="7">
         <v>156</v>
       </c>
-      <c r="AQ6" s="3">
+      <c r="AP6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="7">
         <v>416.64</v>
       </c>
-      <c r="AR6" s="3">
+      <c r="AR6" s="7">
         <v>365.2</v>
       </c>
-      <c r="AS6" s="3">
+      <c r="AS6" s="7">
         <v>1608.34</v>
       </c>
-      <c r="AT6" s="3">
+      <c r="AT6" s="7">
         <v>109.31</v>
       </c>
-      <c r="AU6" s="3">
+      <c r="AU6" s="7">
         <v>1842.2</v>
       </c>
-      <c r="AV6" s="3">
+      <c r="AV6" s="7">
         <v>4940.24</v>
       </c>
-      <c r="AW6" s="3">
+      <c r="AW6" s="7">
         <v>66.38</v>
       </c>
-      <c r="AY6" s="3">
+      <c r="AX6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="7">
         <v>3671.09</v>
       </c>
-      <c r="AZ6" s="3">
+      <c r="AZ6" s="7">
         <v>473.95</v>
       </c>
-      <c r="BA6" s="3">
+      <c r="BA6" s="7">
         <v>5877.39</v>
       </c>
-      <c r="BB6" s="3">
+      <c r="BB6" s="7">
         <v>496.37</v>
       </c>
-      <c r="BC6" s="3">
+      <c r="BC6" s="7">
         <v>9766.5400000000009</v>
       </c>
-      <c r="BD6" s="3">
+      <c r="BD6" s="7">
         <v>455.57</v>
       </c>
-      <c r="BE6" s="3">
+      <c r="BE6" s="7">
         <v>7244.37</v>
       </c>
-      <c r="BF6" s="3">
+      <c r="BF6" s="7">
         <v>469.24</v>
       </c>
-      <c r="BG6" s="3">
+      <c r="BG6" s="7">
         <v>1572.32</v>
       </c>
-      <c r="BI6" s="3">
+      <c r="BH6" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="7">
         <v>5230.33</v>
       </c>
-      <c r="BJ6" s="3">
+      <c r="BJ6" s="7">
         <v>313.66000000000003</v>
       </c>
-      <c r="BK6" s="3">
+      <c r="BK6" s="7">
         <v>4613.38</v>
       </c>
-      <c r="BL6" s="3">
+      <c r="BL6" s="7">
         <v>575.82000000000005</v>
       </c>
-      <c r="BM6" s="3">
+      <c r="BM6" s="7">
         <v>6217.43</v>
       </c>
-      <c r="BO6" s="3">
+      <c r="BN6" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO6" s="7">
         <v>7259.19</v>
       </c>
-      <c r="BP6" s="3">
+      <c r="BP6" s="7">
         <v>144.27000000000001</v>
       </c>
-      <c r="BQ6" s="3">
+      <c r="BQ6" s="7">
         <v>4503.45</v>
       </c>
-      <c r="BR6" s="3">
+      <c r="BR6" s="7">
         <v>260.08999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+      <c r="A7" s="7">
         <v>2104.79</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="7">
         <v>1390.38</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="7">
         <v>9068.5300000000007</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="7">
         <v>2485.69</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="7">
         <v>163.36000000000001</v>
       </c>
-      <c r="G7" s="3">
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
         <v>2428.2600000000002</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="7">
         <v>199.76</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="7">
         <v>204.55</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="7">
         <v>40.840000000000003</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="7">
         <v>575.9</v>
       </c>
-      <c r="M7" s="3">
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7">
         <v>509.16</v>
       </c>
-      <c r="O7" s="3">
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
         <v>310.5</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="7">
         <v>104.13</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="7">
         <v>416.97</v>
       </c>
-      <c r="R7" s="3">
+      <c r="R7" s="7">
         <v>112.05</v>
       </c>
-      <c r="S7" s="3">
+      <c r="S7" s="7">
         <v>873.19</v>
       </c>
-      <c r="T7" s="3">
+      <c r="T7" s="7">
         <v>60.71</v>
       </c>
-      <c r="U7" s="3">
+      <c r="U7" s="7">
         <v>381.26</v>
       </c>
-      <c r="W7" s="3">
+      <c r="V7" s="8">
+        <v>0</v>
+      </c>
+      <c r="W7" s="7">
         <v>224.4</v>
       </c>
-      <c r="X7" s="3">
+      <c r="X7" s="7">
         <v>91.63</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="Y7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="7">
         <v>202.98</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AB7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="7">
         <v>847.85</v>
       </c>
-      <c r="AD7" s="3">
+      <c r="AD7" s="7">
         <v>576.27</v>
       </c>
-      <c r="AE7" s="3">
+      <c r="AE7" s="7">
         <v>212.96</v>
       </c>
-      <c r="AF7" s="3">
+      <c r="AF7" s="7">
         <v>57.7</v>
       </c>
-      <c r="AG7" s="3">
+      <c r="AG7" s="7">
         <v>1556.18</v>
       </c>
-      <c r="AH7" s="3">
+      <c r="AH7" s="7">
         <v>293.77999999999997</v>
       </c>
-      <c r="AI7" s="3">
+      <c r="AI7" s="7">
         <v>224.4</v>
       </c>
-      <c r="AJ7" s="3">
+      <c r="AJ7" s="7">
         <v>91.4</v>
       </c>
-      <c r="AK7" s="3">
+      <c r="AK7" s="7">
         <v>153.88999999999999</v>
       </c>
-      <c r="AL7" s="3">
+      <c r="AL7" s="7">
         <v>100.73</v>
       </c>
-      <c r="AM7" s="3">
+      <c r="AM7" s="7">
         <v>1002.25</v>
       </c>
-      <c r="AO7" s="3">
+      <c r="AN7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="7">
         <v>120.7</v>
       </c>
-      <c r="AQ7" s="3">
+      <c r="AP7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="7">
         <v>329.95</v>
       </c>
-      <c r="AR7" s="3">
+      <c r="AR7" s="7">
         <v>819.04</v>
       </c>
-      <c r="AS7" s="3">
+      <c r="AS7" s="7">
         <v>1100.83</v>
       </c>
-      <c r="AT7" s="3">
+      <c r="AT7" s="7">
         <v>109.31</v>
       </c>
-      <c r="AU7" s="3">
+      <c r="AU7" s="7">
         <v>1833.44</v>
       </c>
-      <c r="AV7" s="3">
+      <c r="AV7" s="7">
         <v>5300.26</v>
       </c>
-      <c r="AW7" s="3">
+      <c r="AW7" s="7">
         <v>41.42</v>
       </c>
-      <c r="AY7" s="3">
+      <c r="AX7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="7">
         <v>2771.97</v>
       </c>
-      <c r="AZ7" s="3">
+      <c r="AZ7" s="7">
         <v>413.19</v>
       </c>
-      <c r="BA7" s="3">
+      <c r="BA7" s="7">
         <v>4067.44</v>
       </c>
-      <c r="BB7" s="3">
+      <c r="BB7" s="7">
         <v>455.35</v>
       </c>
-      <c r="BC7" s="3">
+      <c r="BC7" s="7">
         <v>7018.5</v>
       </c>
-      <c r="BD7" s="3">
+      <c r="BD7" s="7">
         <v>576.41</v>
       </c>
-      <c r="BE7" s="3">
+      <c r="BE7" s="7">
         <v>5801.88</v>
       </c>
-      <c r="BF7" s="3">
+      <c r="BF7" s="7">
         <v>401.82</v>
       </c>
-      <c r="BG7" s="3">
+      <c r="BG7" s="7">
         <v>1482.43</v>
       </c>
-      <c r="BI7" s="3">
+      <c r="BH7" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="7">
         <v>3835.89</v>
       </c>
-      <c r="BJ7" s="3">
+      <c r="BJ7" s="7">
         <v>220.48</v>
       </c>
-      <c r="BK7" s="3">
+      <c r="BK7" s="7">
         <v>3749.07</v>
       </c>
-      <c r="BL7" s="3">
+      <c r="BL7" s="7">
         <v>434.54</v>
       </c>
-      <c r="BM7" s="3">
+      <c r="BM7" s="7">
         <v>3067.94</v>
       </c>
-      <c r="BO7" s="3">
+      <c r="BN7" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO7" s="7">
         <v>3551.53</v>
       </c>
-      <c r="BP7" s="3">
+      <c r="BP7" s="7">
         <v>404.63</v>
       </c>
-      <c r="BQ7" s="3">
+      <c r="BQ7" s="7">
         <v>3517.54</v>
       </c>
-      <c r="BR7" s="3">
+      <c r="BR7" s="7">
         <v>324.77</v>
       </c>
     </row>
     <row r="8" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="A8" s="7">
         <v>2073.91</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="7">
         <v>1600.69</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="7">
         <v>4580.91</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="7">
         <v>2780.72</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="7">
         <v>156.76</v>
       </c>
-      <c r="G8" s="3">
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
         <v>4419.72</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="7">
         <v>296.08999999999997</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="7">
         <v>239.22</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="7">
         <v>51.74</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="7">
         <v>1342.99</v>
       </c>
-      <c r="M8" s="3">
+      <c r="L8" s="8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
         <v>437.24</v>
       </c>
-      <c r="O8" s="3">
+      <c r="N8" s="8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
         <v>321.33999999999997</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="7">
         <v>115.41</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="7">
         <v>414.93</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="7">
         <v>101.81</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="7">
         <v>913.18</v>
       </c>
-      <c r="T8" s="3">
+      <c r="T8" s="7">
         <v>80.069999999999993</v>
       </c>
-      <c r="U8" s="3">
+      <c r="U8" s="7">
         <v>475.54</v>
       </c>
-      <c r="W8" s="3">
+      <c r="V8" s="8">
+        <v>0</v>
+      </c>
+      <c r="W8" s="7">
         <v>159.65</v>
       </c>
-      <c r="X8" s="3">
+      <c r="X8" s="7">
         <v>91.46</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="Y8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="7">
         <v>307.88</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AB8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="7">
         <v>822.28</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AD8" s="7">
         <v>2750.49</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AE8" s="7">
         <v>214.24</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AF8" s="7">
         <v>54.38</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AG8" s="7">
         <v>1225.52</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AH8" s="7">
         <v>246.72</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AI8" s="7">
         <v>243.6</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AJ8" s="7">
         <v>103.43</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AK8" s="7">
         <v>181.43</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AL8" s="7">
         <v>100.73</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AM8" s="7">
         <v>248.6</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AN8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="7">
         <v>82.16</v>
       </c>
-      <c r="AQ8" s="3">
+      <c r="AP8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="7">
         <v>563.74</v>
       </c>
-      <c r="AR8" s="3">
+      <c r="AR8" s="7">
         <v>531.72</v>
       </c>
-      <c r="AS8" s="3">
+      <c r="AS8" s="7">
         <v>765.98</v>
       </c>
-      <c r="AT8" s="3">
+      <c r="AT8" s="7">
         <v>137.38999999999999</v>
       </c>
-      <c r="AU8" s="3">
+      <c r="AU8" s="7">
         <v>1761.68</v>
       </c>
-      <c r="AV8" s="3">
+      <c r="AV8" s="7">
         <v>6893.5</v>
       </c>
-      <c r="AW8" s="3">
+      <c r="AW8" s="7">
         <v>62.92</v>
       </c>
-      <c r="AY8" s="3">
+      <c r="AX8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="7">
         <v>2800.1</v>
       </c>
-      <c r="AZ8" s="3">
+      <c r="AZ8" s="7">
         <v>413.46</v>
       </c>
-      <c r="BA8" s="3">
+      <c r="BA8" s="7">
         <v>4228.67</v>
       </c>
-      <c r="BB8" s="3">
+      <c r="BB8" s="7">
         <v>555.41999999999996</v>
       </c>
-      <c r="BC8" s="3">
+      <c r="BC8" s="7">
         <v>5891.98</v>
       </c>
-      <c r="BD8" s="3">
+      <c r="BD8" s="7">
         <v>765.41</v>
       </c>
-      <c r="BE8" s="3">
+      <c r="BE8" s="7">
         <v>4996.1499999999996</v>
       </c>
-      <c r="BF8" s="3">
+      <c r="BF8" s="7">
         <v>387.48</v>
       </c>
-      <c r="BG8" s="3">
+      <c r="BG8" s="7">
         <v>1664.53</v>
       </c>
-      <c r="BI8" s="3">
+      <c r="BH8" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI8" s="7">
         <v>2480.17</v>
       </c>
-      <c r="BJ8" s="3">
+      <c r="BJ8" s="7">
         <v>271.24</v>
       </c>
-      <c r="BK8" s="3">
+      <c r="BK8" s="7">
         <v>3363.72</v>
       </c>
-      <c r="BL8" s="3">
+      <c r="BL8" s="7">
         <v>535.39</v>
       </c>
-      <c r="BM8" s="3">
+      <c r="BM8" s="7">
         <v>2276.4</v>
       </c>
-      <c r="BO8" s="3">
+      <c r="BN8" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO8" s="7">
         <v>3577.63</v>
       </c>
-      <c r="BP8" s="3">
+      <c r="BP8" s="7">
         <v>362.47</v>
       </c>
-      <c r="BQ8" s="3">
+      <c r="BQ8" s="7">
         <v>2968.98</v>
       </c>
-      <c r="BR8" s="3">
+      <c r="BR8" s="7">
         <v>583.16</v>
       </c>
     </row>
     <row r="9" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="7">
         <v>2174.6</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="7">
         <v>1184.71</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="7">
         <v>8311.14</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="7">
         <v>2927.08</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="7">
         <v>116.52</v>
       </c>
-      <c r="G9" s="3">
+      <c r="F9" s="8">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7">
         <v>4932.04</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="7">
         <v>453.43</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="7">
         <v>232.35</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="7">
         <v>46.7</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="7">
         <v>1346.31</v>
       </c>
-      <c r="M9" s="3">
+      <c r="L9" s="8">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7">
         <v>380.86</v>
       </c>
-      <c r="O9" s="3">
+      <c r="N9" s="8">
+        <v>0</v>
+      </c>
+      <c r="O9" s="7">
         <v>370.08</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="7">
         <v>127.35</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="7">
         <v>421.03</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="7">
         <v>102.09</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="7">
         <v>533.37</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="7">
         <v>64.66</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="7">
         <v>476.64</v>
       </c>
-      <c r="W9" s="3">
+      <c r="V9" s="8">
+        <v>0</v>
+      </c>
+      <c r="W9" s="7">
         <v>173.98</v>
       </c>
-      <c r="X9" s="3">
+      <c r="X9" s="7">
         <v>231.32</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="Y9" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="7">
         <v>284.51</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AB9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="7">
         <v>840.15</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AD9" s="7">
         <v>1672.56</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AE9" s="7">
         <v>221.62</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AF9" s="7">
         <v>54.38</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AG9" s="7">
         <v>1243.27</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AH9" s="7">
         <v>262.35000000000002</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AI9" s="7">
         <v>234.89</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AJ9" s="7">
         <v>103.43</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AK9" s="7">
         <v>182.26</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AL9" s="7">
         <v>100.73</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AM9" s="7">
         <v>18.170000000000002</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AN9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="7">
         <v>137.91999999999999</v>
       </c>
-      <c r="AQ9" s="3">
+      <c r="AP9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="7">
         <v>475.24</v>
       </c>
-      <c r="AR9" s="3">
+      <c r="AR9" s="7">
         <v>311.86</v>
       </c>
-      <c r="AS9" s="3">
+      <c r="AS9" s="7">
         <v>649.28</v>
       </c>
-      <c r="AT9" s="3">
+      <c r="AT9" s="7">
         <v>109.31</v>
       </c>
-      <c r="AU9" s="3">
+      <c r="AU9" s="7">
         <v>1899.41</v>
       </c>
-      <c r="AV9" s="3">
+      <c r="AV9" s="7">
         <v>4791.8900000000003</v>
       </c>
-      <c r="AW9" s="3">
+      <c r="AW9" s="7">
         <v>41.42</v>
       </c>
-      <c r="AY9" s="3">
+      <c r="AX9" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="7">
         <v>1867.35</v>
       </c>
-      <c r="AZ9" s="3">
+      <c r="AZ9" s="7">
         <v>353.09</v>
       </c>
-      <c r="BA9" s="3">
+      <c r="BA9" s="7">
         <v>3230.38</v>
       </c>
-      <c r="BB9" s="3">
+      <c r="BB9" s="7">
         <v>393.65</v>
       </c>
-      <c r="BC9" s="3">
+      <c r="BC9" s="7">
         <v>3842.35</v>
       </c>
-      <c r="BD9" s="3">
+      <c r="BD9" s="7">
         <v>1011.38</v>
       </c>
-      <c r="BE9" s="3">
+      <c r="BE9" s="7">
         <v>3970.16</v>
       </c>
-      <c r="BF9" s="3">
+      <c r="BF9" s="7">
         <v>363.07</v>
       </c>
-      <c r="BG9" s="3">
+      <c r="BG9" s="7">
         <v>1789.07</v>
       </c>
-      <c r="BI9" s="3">
+      <c r="BH9" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="7">
         <v>1743.83</v>
       </c>
-      <c r="BJ9" s="3">
+      <c r="BJ9" s="7">
         <v>231.72</v>
       </c>
-      <c r="BK9" s="3">
+      <c r="BK9" s="7">
         <v>2416.27</v>
       </c>
-      <c r="BL9" s="3">
+      <c r="BL9" s="7">
         <v>474.38</v>
       </c>
-      <c r="BM9" s="3">
+      <c r="BM9" s="7">
         <v>2349.8000000000002</v>
       </c>
-      <c r="BO9" s="3">
+      <c r="BN9" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO9" s="7">
         <v>2651.93</v>
       </c>
-      <c r="BP9" s="3">
+      <c r="BP9" s="7">
         <v>471.93</v>
       </c>
-      <c r="BQ9" s="3">
+      <c r="BQ9" s="7">
         <v>3292.19</v>
       </c>
-      <c r="BR9" s="3">
+      <c r="BR9" s="7">
         <v>273.02</v>
       </c>
     </row>
     <row r="10" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="A10" s="7">
         <v>2087.9899999999998</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="7">
         <v>1846.82</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="7">
         <v>2870.94</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="7">
         <v>143.28</v>
       </c>
-      <c r="G10" s="3">
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7">
         <v>5077.96</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="7">
         <v>433.66</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="7">
         <v>230.05</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="7">
         <v>46.7</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="7">
         <v>788.75</v>
       </c>
-      <c r="M10" s="3">
+      <c r="L10" s="8">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7">
         <v>379.87</v>
       </c>
-      <c r="O10" s="3">
+      <c r="N10" s="8">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7">
         <v>370.08</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="7">
         <v>127.42</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="7">
         <v>472.6</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="7">
         <v>86.54</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="7">
         <v>509.37</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="7">
         <v>68.62</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="7">
         <v>500.01</v>
       </c>
-      <c r="W10" s="3">
+      <c r="V10" s="8">
+        <v>0</v>
+      </c>
+      <c r="W10" s="7">
         <v>202.4</v>
       </c>
-      <c r="X10" s="3">
+      <c r="X10" s="7">
         <v>199.24</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="Y10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="7">
         <v>273.49</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AB10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="7">
         <v>672.58</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AD10" s="7">
         <v>399.43</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AE10" s="7">
         <v>208.91</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AF10" s="7">
         <v>58.07</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AG10" s="7">
         <v>1425.43</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AH10" s="7">
         <v>278.04000000000002</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AI10" s="7">
         <v>268.56</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AJ10" s="7">
         <v>103.51</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AK10" s="7">
         <v>138.01</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AL10" s="7">
         <v>100.73</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AM10" s="7">
         <v>1154.02</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AN10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="7">
         <v>114.94</v>
       </c>
-      <c r="AQ10" s="3">
+      <c r="AP10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="7">
         <v>597.86</v>
       </c>
-      <c r="AR10" s="3">
+      <c r="AR10" s="7">
         <v>178.56</v>
       </c>
-      <c r="AS10" s="3">
+      <c r="AS10" s="7">
         <v>651.79</v>
       </c>
-      <c r="AT10" s="3">
+      <c r="AT10" s="7">
         <v>109.31</v>
       </c>
-      <c r="AU10" s="3">
+      <c r="AU10" s="7">
         <v>2012.75</v>
       </c>
-      <c r="AV10" s="3">
+      <c r="AV10" s="7">
         <v>5746.58</v>
       </c>
-      <c r="AW10" s="3">
+      <c r="AW10" s="7">
         <v>70.38</v>
       </c>
-      <c r="AY10" s="3">
+      <c r="AX10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="7">
         <v>2308.2199999999998</v>
       </c>
-      <c r="AZ10" s="3">
+      <c r="AZ10" s="7">
         <v>353.2</v>
       </c>
-      <c r="BA10" s="3">
+      <c r="BA10" s="7">
         <v>4494.3500000000004</v>
       </c>
-      <c r="BB10" s="3">
+      <c r="BB10" s="7">
         <v>495.13</v>
       </c>
-      <c r="BC10" s="3">
+      <c r="BC10" s="7">
         <v>4241.04</v>
       </c>
-      <c r="BD10" s="3">
+      <c r="BD10" s="7">
         <v>1353.95</v>
       </c>
-      <c r="BE10" s="3">
+      <c r="BE10" s="7">
         <v>3688.57</v>
       </c>
-      <c r="BF10" s="3">
+      <c r="BF10" s="7">
         <v>459.45</v>
       </c>
-      <c r="BG10" s="3">
+      <c r="BG10" s="7">
         <v>1770.2</v>
       </c>
-      <c r="BI10" s="3">
+      <c r="BH10" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="7">
         <v>1650.71</v>
       </c>
-      <c r="BJ10" s="3">
+      <c r="BJ10" s="7">
         <v>434.43</v>
       </c>
-      <c r="BK10" s="3">
+      <c r="BK10" s="7">
         <v>2549.2199999999998</v>
       </c>
-      <c r="BL10" s="3">
+      <c r="BL10" s="7">
         <v>636.41999999999996</v>
       </c>
-      <c r="BM10" s="3">
+      <c r="BM10" s="7">
         <v>2449.94</v>
       </c>
-      <c r="BO10" s="3">
+      <c r="BN10" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO10" s="7">
         <v>2960.7</v>
       </c>
-      <c r="BP10" s="3">
+      <c r="BP10" s="7">
         <v>317.45999999999998</v>
       </c>
-      <c r="BQ10" s="3">
+      <c r="BQ10" s="7">
         <v>4186.33</v>
       </c>
-      <c r="BR10" s="3">
+      <c r="BR10" s="7">
         <v>351.45</v>
       </c>
     </row>
     <row r="11" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="A11" s="7">
         <v>2228.27</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="7">
         <v>496.84</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="7">
         <v>3140.38</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="7">
         <v>146.47999999999999</v>
       </c>
-      <c r="G11" s="3">
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
         <v>6341.29</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="7">
         <v>555.44000000000005</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="7">
         <v>241.24</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="7">
         <v>43.76</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="7">
         <v>559.69000000000005</v>
       </c>
-      <c r="M11" s="3">
+      <c r="L11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7">
         <v>475.28</v>
       </c>
-      <c r="O11" s="3">
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+      <c r="O11" s="7">
         <v>347.18</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="7">
         <v>139.41</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="7">
         <v>488.23</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="7">
         <v>120.07</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11" s="7">
         <v>636.42999999999995</v>
       </c>
-      <c r="T11" s="3">
+      <c r="T11" s="7">
         <v>77.27</v>
       </c>
-      <c r="U11" s="3">
+      <c r="U11" s="7">
         <v>501.06</v>
       </c>
-      <c r="W11" s="3">
+      <c r="V11" s="8">
+        <v>0</v>
+      </c>
+      <c r="W11" s="7">
         <v>211.1</v>
       </c>
-      <c r="X11" s="3">
+      <c r="X11" s="7">
         <v>104.1</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="Y11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="7">
         <v>261.83999999999997</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AB11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="7">
         <v>1035.03</v>
       </c>
-      <c r="AD11" s="3">
+      <c r="AD11" s="7">
         <v>284.14999999999998</v>
       </c>
-      <c r="AE11" s="3">
+      <c r="AE11" s="7">
         <v>218.97</v>
       </c>
-      <c r="AF11" s="3">
+      <c r="AF11" s="7">
         <v>58.07</v>
       </c>
-      <c r="AG11" s="3">
+      <c r="AG11" s="7">
         <v>1448.01</v>
       </c>
-      <c r="AH11" s="3">
+      <c r="AH11" s="7">
         <v>580.46</v>
       </c>
-      <c r="AI11" s="3">
+      <c r="AI11" s="7">
         <v>259.44</v>
       </c>
-      <c r="AJ11" s="3">
+      <c r="AJ11" s="7">
         <v>103.53</v>
       </c>
-      <c r="AK11" s="3">
+      <c r="AK11" s="7">
         <v>184.85</v>
       </c>
-      <c r="AL11" s="3">
+      <c r="AL11" s="7">
         <v>100.73</v>
       </c>
-      <c r="AM11" s="3">
+      <c r="AM11" s="7">
         <v>249.95</v>
       </c>
-      <c r="AO11" s="3">
+      <c r="AN11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="7">
         <v>76.05</v>
       </c>
-      <c r="AQ11" s="3">
+      <c r="AP11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="7">
         <v>797.31</v>
       </c>
-      <c r="AR11" s="3">
+      <c r="AR11" s="7">
         <v>279.86</v>
       </c>
-      <c r="AS11" s="3">
+      <c r="AS11" s="7">
         <v>1085.44</v>
       </c>
-      <c r="AT11" s="3">
+      <c r="AT11" s="7">
         <v>109.31</v>
       </c>
-      <c r="AU11" s="3">
+      <c r="AU11" s="7">
         <v>2023.45</v>
       </c>
-      <c r="AV11" s="3">
+      <c r="AV11" s="7">
         <v>7240.16</v>
       </c>
-      <c r="AW11" s="3">
+      <c r="AW11" s="7">
         <v>41.18</v>
       </c>
-      <c r="AY11" s="3">
+      <c r="AX11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="7">
         <v>3271.92</v>
       </c>
-      <c r="AZ11" s="3">
+      <c r="AZ11" s="7">
         <v>413.65</v>
       </c>
-      <c r="BA11" s="3">
+      <c r="BA11" s="7">
         <v>6121.49</v>
       </c>
-      <c r="BB11" s="3">
+      <c r="BB11" s="7">
         <v>535.08000000000004</v>
       </c>
-      <c r="BC11" s="3">
+      <c r="BC11" s="7">
         <v>5626.81</v>
       </c>
-      <c r="BD11" s="3">
+      <c r="BD11" s="7">
         <v>766.61</v>
       </c>
-      <c r="BE11" s="3">
+      <c r="BE11" s="7">
         <v>3775.22</v>
       </c>
-      <c r="BF11" s="3">
+      <c r="BF11" s="7">
         <v>676.78</v>
       </c>
-      <c r="BG11" s="3">
+      <c r="BG11" s="7">
         <v>1903.44</v>
       </c>
-      <c r="BI11" s="3">
+      <c r="BH11" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="7">
         <v>3021.17</v>
       </c>
-      <c r="BJ11" s="3">
+      <c r="BJ11" s="7">
         <v>395.21</v>
       </c>
-      <c r="BK11" s="3">
+      <c r="BK11" s="7">
         <v>3613.16</v>
       </c>
-      <c r="BL11" s="3">
+      <c r="BL11" s="7">
         <v>595.88</v>
       </c>
-      <c r="BM11" s="3">
+      <c r="BM11" s="7">
         <v>2694.07</v>
       </c>
-      <c r="BO11" s="3">
+      <c r="BN11" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO11" s="7">
         <v>5232.16</v>
       </c>
-      <c r="BP11" s="3">
+      <c r="BP11" s="7">
         <v>489.55</v>
       </c>
-      <c r="BQ11" s="3">
+      <c r="BQ11" s="7">
         <v>5379.52</v>
       </c>
-      <c r="BR11" s="3">
+      <c r="BR11" s="7">
         <v>311.83999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="A12" s="7">
         <v>2307.17</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="7">
         <v>1156.29</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="7">
         <v>2919.93</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="7">
         <v>184.6</v>
       </c>
-      <c r="G12" s="3">
+      <c r="F12" s="8">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7">
         <v>7680.95</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="7">
         <v>533.5</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="7">
         <v>260.27</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="7">
         <v>43.76</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="7">
         <v>1328.25</v>
       </c>
-      <c r="M12" s="3">
+      <c r="L12" s="8">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7">
         <v>673.25</v>
       </c>
-      <c r="O12" s="3">
+      <c r="N12" s="8">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7">
         <v>339.05</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="7">
         <v>150.83000000000001</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="7">
         <v>424.8</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12" s="7">
         <v>171.72</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="7">
         <v>977.94</v>
       </c>
-      <c r="T12" s="3">
+      <c r="T12" s="7">
         <v>85.93</v>
       </c>
-      <c r="U12" s="3">
+      <c r="U12" s="7">
         <v>504.85</v>
       </c>
-      <c r="W12" s="3">
+      <c r="V12" s="8">
+        <v>0</v>
+      </c>
+      <c r="W12" s="7">
         <v>237.98</v>
       </c>
-      <c r="X12" s="3">
+      <c r="X12" s="7">
         <v>126.99</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="Y12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="7">
         <v>283.41000000000003</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AB12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="7">
         <v>1179.8800000000001</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AD12" s="7">
         <v>263.08999999999997</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AE12" s="7">
         <v>411.81</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AF12" s="7">
         <v>120</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AG12" s="7">
         <v>1494.64</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AH12" s="7">
         <v>387.83</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AI12" s="7">
         <v>266.45999999999998</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AJ12" s="7">
         <v>103.15</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AK12" s="7">
         <v>173.26</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AL12" s="7">
         <v>100.73</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AM12" s="7">
         <v>1173.99</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AN12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="7">
         <v>149.22999999999999</v>
       </c>
-      <c r="AQ12" s="3">
+      <c r="AP12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="7">
         <v>958.15</v>
       </c>
-      <c r="AR12" s="3">
+      <c r="AR12" s="7">
         <v>140.47999999999999</v>
       </c>
-      <c r="AS12" s="3">
+      <c r="AS12" s="7">
         <v>1733.12</v>
       </c>
-      <c r="AT12" s="3">
+      <c r="AT12" s="7">
         <v>109.31</v>
       </c>
-      <c r="AU12" s="3">
+      <c r="AU12" s="7">
         <v>2315</v>
       </c>
-      <c r="AV12" s="3">
+      <c r="AV12" s="7">
         <v>6708.37</v>
       </c>
-      <c r="AW12" s="3">
+      <c r="AW12" s="7">
         <v>77.430000000000007</v>
       </c>
-      <c r="AY12" s="3">
+      <c r="AX12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="7">
         <v>3571.92</v>
       </c>
-      <c r="AZ12" s="3">
+      <c r="AZ12" s="7">
         <v>452.67</v>
       </c>
-      <c r="BA12" s="3">
+      <c r="BA12" s="7">
         <v>6442.93</v>
       </c>
-      <c r="BB12" s="3">
+      <c r="BB12" s="7">
         <v>695.17</v>
       </c>
-      <c r="BC12" s="3">
+      <c r="BC12" s="7">
         <v>7325.89</v>
       </c>
-      <c r="BD12" s="3">
+      <c r="BD12" s="7">
         <v>553.71</v>
       </c>
-      <c r="BE12" s="3">
+      <c r="BE12" s="7">
         <v>7239.95</v>
       </c>
-      <c r="BF12" s="3">
+      <c r="BF12" s="7">
         <v>562.79</v>
       </c>
-      <c r="BG12" s="3">
+      <c r="BG12" s="7">
         <v>1880.31</v>
       </c>
-      <c r="BI12" s="3">
+      <c r="BH12" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="7">
         <v>4770</v>
       </c>
-      <c r="BJ12" s="3">
+      <c r="BJ12" s="7">
         <v>319.72000000000003</v>
       </c>
-      <c r="BK12" s="3">
+      <c r="BK12" s="7">
         <v>5749.78</v>
       </c>
-      <c r="BL12" s="3">
+      <c r="BL12" s="7">
         <v>654.76</v>
       </c>
-      <c r="BM12" s="3">
+      <c r="BM12" s="7">
         <v>2632.49</v>
       </c>
-      <c r="BO12" s="3">
+      <c r="BN12" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO12" s="7">
         <v>7514.35</v>
       </c>
-      <c r="BP12" s="3">
+      <c r="BP12" s="7">
         <v>471.86</v>
       </c>
-      <c r="BQ12" s="3">
+      <c r="BQ12" s="7">
         <v>5391.23</v>
       </c>
-      <c r="BR12" s="3">
+      <c r="BR12" s="7">
         <v>298.89999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="A13" s="7">
         <v>2295.98</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="7">
         <v>83.28</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="7">
         <v>148.09</v>
       </c>
-      <c r="G13" s="3">
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7">
         <v>7932.94</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="7">
         <v>512.75</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="7">
         <v>227.02</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="7">
         <v>43.76</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="7">
         <v>777.2</v>
       </c>
-      <c r="M13" s="3">
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7">
         <v>571.54</v>
       </c>
-      <c r="O13" s="3">
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+      <c r="O13" s="7">
         <v>314.86</v>
       </c>
-      <c r="P13" s="3">
+      <c r="P13" s="7">
         <v>138.91</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="Q13" s="7">
         <v>464.24</v>
       </c>
-      <c r="R13" s="3">
+      <c r="R13" s="7">
         <v>166.23</v>
       </c>
-      <c r="S13" s="3">
+      <c r="S13" s="7">
         <v>1021.14</v>
       </c>
-      <c r="T13" s="3">
+      <c r="T13" s="7">
         <v>77.27</v>
       </c>
-      <c r="U13" s="3">
+      <c r="U13" s="7">
         <v>541.39</v>
       </c>
-      <c r="W13" s="3">
+      <c r="V13" s="8">
+        <v>0</v>
+      </c>
+      <c r="W13" s="7">
         <v>260.68</v>
       </c>
-      <c r="X13" s="3">
+      <c r="X13" s="7">
         <v>103.02</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="Y13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="7">
         <v>271.8</v>
       </c>
-      <c r="AC13" s="3">
+      <c r="AB13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="7">
         <v>1038.9100000000001</v>
       </c>
-      <c r="AD13" s="3">
+      <c r="AD13" s="7">
         <v>935.84</v>
       </c>
-      <c r="AE13" s="3">
+      <c r="AE13" s="7">
         <v>301.18</v>
       </c>
-      <c r="AF13" s="3">
+      <c r="AF13" s="7">
         <v>58.07</v>
       </c>
-      <c r="AG13" s="3">
+      <c r="AG13" s="7">
         <v>1754.83</v>
       </c>
-      <c r="AH13" s="3">
+      <c r="AH13" s="7">
         <v>185.89</v>
       </c>
-      <c r="AI13" s="3">
+      <c r="AI13" s="7">
         <v>227.36</v>
       </c>
-      <c r="AJ13" s="3">
+      <c r="AJ13" s="7">
         <v>126.99</v>
       </c>
-      <c r="AK13" s="3">
+      <c r="AK13" s="7">
         <v>155.86000000000001</v>
       </c>
-      <c r="AL13" s="3">
+      <c r="AL13" s="7">
         <v>100.73</v>
       </c>
-      <c r="AM13" s="3">
+      <c r="AM13" s="7">
         <v>187.32</v>
       </c>
-      <c r="AO13" s="3">
+      <c r="AN13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="7">
         <v>88.11</v>
       </c>
-      <c r="AQ13" s="3">
+      <c r="AP13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="7">
         <v>678.53</v>
       </c>
-      <c r="AR13" s="3">
+      <c r="AR13" s="7">
         <v>208.55</v>
       </c>
-      <c r="AS13" s="3">
+      <c r="AS13" s="7">
         <v>1259.05</v>
       </c>
-      <c r="AT13" s="3">
+      <c r="AT13" s="7">
         <v>115.79</v>
       </c>
-      <c r="AU13" s="3">
+      <c r="AU13" s="7">
         <v>1983.39</v>
       </c>
-      <c r="AV13" s="3">
+      <c r="AV13" s="7">
         <v>5729.08</v>
       </c>
-      <c r="AW13" s="3">
+      <c r="AW13" s="7">
         <v>41.18</v>
       </c>
-      <c r="AY13" s="3">
+      <c r="AX13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="7">
         <v>3470.87</v>
       </c>
-      <c r="AZ13" s="3">
+      <c r="AZ13" s="7">
         <v>432.46</v>
       </c>
-      <c r="BA13" s="3">
+      <c r="BA13" s="7">
         <v>7398.59</v>
       </c>
-      <c r="BB13" s="3">
+      <c r="BB13" s="7">
         <v>472.34</v>
       </c>
-      <c r="BC13" s="3">
+      <c r="BC13" s="7">
         <v>6919.7</v>
       </c>
-      <c r="BD13" s="3">
+      <c r="BD13" s="7">
         <v>594.12</v>
       </c>
-      <c r="BE13" s="3">
+      <c r="BE13" s="7">
         <v>6728.66</v>
       </c>
-      <c r="BF13" s="3">
+      <c r="BF13" s="7">
         <v>760.52</v>
       </c>
-      <c r="BG13" s="3">
+      <c r="BG13" s="7">
         <v>1646.17</v>
       </c>
-      <c r="BI13" s="3">
+      <c r="BH13" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI13" s="7">
         <v>4346.78</v>
       </c>
-      <c r="BJ13" s="3">
+      <c r="BJ13" s="7">
         <v>304.64</v>
       </c>
-      <c r="BK13" s="3">
+      <c r="BK13" s="7">
         <v>4779.03</v>
       </c>
-      <c r="BL13" s="3">
+      <c r="BL13" s="7">
         <v>492.5</v>
       </c>
-      <c r="BM13" s="3">
+      <c r="BM13" s="7">
         <v>2428.5100000000002</v>
       </c>
-      <c r="BO13" s="3">
+      <c r="BN13" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO13" s="7">
         <v>6858.39</v>
       </c>
-      <c r="BP13" s="3">
+      <c r="BP13" s="7">
         <v>573.41</v>
       </c>
-      <c r="BQ13" s="3">
+      <c r="BQ13" s="7">
         <v>5033.12</v>
       </c>
-      <c r="BR13" s="3">
+      <c r="BR13" s="7">
         <v>430.59</v>
       </c>
     </row>
     <row r="14" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+      <c r="A14" s="7">
         <v>2639.14</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="7">
         <v>886.85</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="7">
         <v>123.07</v>
       </c>
-      <c r="G14" s="3">
+      <c r="F14" s="8">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7">
         <v>7286.1</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="7">
         <v>472.87</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="7">
         <v>233.76</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="7">
         <v>46.7</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="7">
         <v>1376.06</v>
       </c>
-      <c r="M14" s="3">
+      <c r="L14" s="8">
+        <v>0</v>
+      </c>
+      <c r="M14" s="7">
         <v>584.34</v>
       </c>
-      <c r="O14" s="3">
+      <c r="N14" s="8">
+        <v>0</v>
+      </c>
+      <c r="O14" s="7">
         <v>334.43</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="7">
         <v>182.91</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="7">
         <v>195.36</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="7">
         <v>64.66</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="7">
         <v>342.65</v>
       </c>
-      <c r="X14" s="3">
+      <c r="V14" s="8">
+        <v>0</v>
+      </c>
+      <c r="X14" s="7">
         <v>91.22</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="Y14" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="7">
         <v>213.72</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AB14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="7">
         <v>1065.29</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="7">
         <v>51.52</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="7">
         <v>512.04</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="7">
         <v>1696.4</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="7">
         <v>278.04000000000002</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="7">
         <v>240.61</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="7">
         <v>126.99</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AK14" s="7">
         <v>185.7</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AL14" s="7">
         <v>100.73</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AM14" s="7">
         <v>834.77</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AN14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="7">
         <v>81.53</v>
       </c>
-      <c r="AQ14" s="3">
+      <c r="AP14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="7">
         <v>795.12</v>
       </c>
-      <c r="AR14" s="3">
+      <c r="AR14" s="7">
         <v>198.55</v>
       </c>
-      <c r="AS14" s="3">
+      <c r="AS14" s="7">
         <v>1493.26</v>
       </c>
-      <c r="AT14" s="3">
+      <c r="AT14" s="7">
         <v>118.67</v>
       </c>
-      <c r="AU14" s="3">
+      <c r="AU14" s="7">
         <v>2075.35</v>
       </c>
-      <c r="AV14" s="3">
+      <c r="AV14" s="7">
         <v>3912.66</v>
       </c>
-      <c r="AW14" s="3">
+      <c r="AW14" s="7">
         <v>77.430000000000007</v>
       </c>
-      <c r="AY14" s="3">
+      <c r="AX14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="7">
         <v>3426.64</v>
       </c>
-      <c r="AZ14" s="3">
+      <c r="AZ14" s="7">
         <v>371.82</v>
       </c>
-      <c r="BA14" s="3">
+      <c r="BA14" s="7">
         <v>8147.61</v>
       </c>
-      <c r="BB14" s="3">
+      <c r="BB14" s="7">
         <v>431.43</v>
       </c>
-      <c r="BC14" s="3">
+      <c r="BC14" s="7">
         <v>8463.16</v>
       </c>
-      <c r="BD14" s="3">
+      <c r="BD14" s="7">
         <v>553.71</v>
       </c>
-      <c r="BE14" s="3">
+      <c r="BE14" s="7">
         <v>8106.91</v>
       </c>
-      <c r="BF14" s="3">
+      <c r="BF14" s="7">
         <v>694.42</v>
       </c>
-      <c r="BG14" s="3">
+      <c r="BG14" s="7">
         <v>1846.36</v>
       </c>
-      <c r="BI14" s="3">
+      <c r="BH14" s="8">
+        <v>0</v>
+      </c>
+      <c r="BI14" s="7">
         <v>4287.1499999999996</v>
       </c>
-      <c r="BJ14" s="3">
+      <c r="BJ14" s="7">
         <v>259.33999999999997</v>
       </c>
-      <c r="BK14" s="3">
+      <c r="BK14" s="7">
         <v>5633.69</v>
       </c>
-      <c r="BL14" s="3">
+      <c r="BL14" s="7">
         <v>594.12</v>
       </c>
-      <c r="BM14" s="3">
+      <c r="BM14" s="7">
         <v>3454.57</v>
       </c>
-      <c r="BO14" s="3">
+      <c r="BN14" s="8">
+        <v>0</v>
+      </c>
+      <c r="BO14" s="7">
         <v>7142.42</v>
       </c>
-      <c r="BP14" s="3">
+      <c r="BP14" s="7">
         <v>436.06</v>
       </c>
-      <c r="BQ14" s="3">
+      <c r="BQ14" s="7">
         <v>6183.42</v>
       </c>
-      <c r="BR14" s="3">
+      <c r="BR14" s="7">
         <v>369.84</v>
       </c>
     </row>
     <row r="15" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="K15" s="3">
+      <c r="K15" s="7">
         <v>438.17</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AM15" s="7">
         <v>142.22</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AO15" s="7">
         <v>83.76</v>
       </c>
-      <c r="AV15" s="3">
+      <c r="AV15" s="7">
         <v>4417.1099999999997</v>
       </c>
-      <c r="AW15" s="3">
+      <c r="AW15" s="7">
         <v>40.840000000000003</v>
       </c>
-      <c r="BP15" s="3">
+      <c r="BP15" s="7">
         <v>487.11</v>
       </c>
     </row>
     <row r="16" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="K16" s="3">
+      <c r="K16" s="7">
         <v>1267.21</v>
       </c>
-      <c r="AM16" s="3">
+      <c r="AM16" s="7">
         <v>838.33</v>
       </c>
-      <c r="AO16" s="3">
+      <c r="AO16" s="7">
         <v>42.68</v>
       </c>
-      <c r="AW16" s="3">
+      <c r="AW16" s="7">
         <v>40.840000000000003</v>
       </c>
     </row>
     <row r="17" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K17" s="3">
+      <c r="K17" s="7">
         <v>785.96</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AM17" s="7">
         <v>51.09</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AO17" s="7">
         <v>80.599999999999994</v>
       </c>
-      <c r="AW17" s="3">
+      <c r="AW17" s="7">
         <v>67.040000000000006</v>
       </c>
     </row>
     <row r="18" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K18" s="3">
+      <c r="K18" s="7">
         <v>1274.58</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AM18" s="7">
         <v>660.44</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AO18" s="7">
         <v>82.73</v>
       </c>
-      <c r="AW18" s="3">
+      <c r="AW18" s="7">
         <v>60.5</v>
       </c>
     </row>
     <row r="19" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K19" s="3">
+      <c r="K19" s="7">
         <v>467.02</v>
       </c>
-      <c r="AM19" s="3">
+      <c r="AM19" s="7">
         <v>46.31</v>
       </c>
-      <c r="AO19" s="3">
+      <c r="AO19" s="7">
         <v>67.819999999999993</v>
       </c>
-      <c r="AW19" s="3">
+      <c r="AW19" s="7">
         <v>41.47</v>
       </c>
     </row>
     <row r="20" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K20" s="3">
+      <c r="K20" s="7">
         <v>1252.97</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AM20" s="7">
         <v>662.44</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AO20" s="7">
         <v>48.82</v>
       </c>
-      <c r="AW20" s="3">
+      <c r="AW20" s="7">
         <v>52.48</v>
       </c>
     </row>
     <row r="21" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K21" s="3">
+      <c r="K21" s="7">
         <v>665.39</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AM21" s="7">
         <v>47.73</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AO21" s="7">
         <v>62.62</v>
       </c>
-      <c r="AW21" s="3">
+      <c r="AW21" s="7">
         <v>41.47</v>
       </c>
     </row>
     <row r="22" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K22" s="3">
+      <c r="K22" s="7">
         <v>1226.92</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AM22" s="7">
         <v>879.41</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AO22" s="7">
         <v>46.96</v>
       </c>
-      <c r="AW22" s="3">
+      <c r="AW22" s="7">
         <v>52.48</v>
       </c>
     </row>
     <row r="23" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K23" s="3">
+      <c r="K23" s="7">
         <v>668.28</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AM23" s="7">
         <v>137.68</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AO23" s="7">
         <v>86.97</v>
       </c>
-      <c r="AW23" s="3">
+      <c r="AW23" s="7">
         <v>43.65</v>
       </c>
     </row>
     <row r="24" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K24" s="3">
+      <c r="K24" s="7">
         <v>547.73</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AM24" s="7">
         <v>264.04000000000002</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AO24" s="7">
         <v>69.14</v>
       </c>
-      <c r="AW24" s="3">
+      <c r="AW24" s="7">
         <v>55.77</v>
       </c>
     </row>
     <row r="25" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K25" s="3">
+      <c r="K25" s="7">
         <v>1307.93</v>
       </c>
-      <c r="AM25" s="3">
+      <c r="AM25" s="7">
         <v>1059.93</v>
       </c>
-      <c r="AO25" s="3">
+      <c r="AO25" s="7">
         <v>90.95</v>
       </c>
-      <c r="AW25" s="3">
+      <c r="AW25" s="7">
         <v>43.65</v>
       </c>
     </row>
     <row r="26" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K26" s="3">
+      <c r="K26" s="7">
         <v>1418.37</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AM26" s="7">
         <v>899.5</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AO26" s="7">
         <v>50.04</v>
       </c>
-      <c r="AW26" s="3">
+      <c r="AW26" s="7">
         <v>63.63</v>
       </c>
     </row>
     <row r="27" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K27" s="3">
+      <c r="K27" s="7">
         <v>545.42999999999995</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AM27" s="7">
         <v>189.75</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AO27" s="7">
         <v>73.510000000000005</v>
       </c>
-      <c r="AW27" s="3">
+      <c r="AW27" s="7">
         <v>46.31</v>
       </c>
     </row>
     <row r="28" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K28" s="3">
+      <c r="K28" s="7">
         <v>1379.15</v>
       </c>
-      <c r="AM28" s="3">
+      <c r="AM28" s="7">
         <v>945.76</v>
       </c>
-      <c r="AO28" s="3">
+      <c r="AO28" s="7">
         <v>52.77</v>
       </c>
-      <c r="AW28" s="3">
+      <c r="AW28" s="7">
         <v>61.47</v>
       </c>
     </row>
     <row r="29" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K29" s="3">
+      <c r="K29" s="7">
         <v>747.37</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AM29" s="7">
         <v>181.63</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AO29" s="7">
         <v>94.23</v>
       </c>
-      <c r="AW29" s="3">
+      <c r="AW29" s="7">
         <v>46.31</v>
       </c>
     </row>
     <row r="30" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K30" s="3">
+      <c r="K30" s="7">
         <v>1270.77</v>
       </c>
-      <c r="AO30" s="3">
+      <c r="AO30" s="7">
         <v>75.36</v>
       </c>
-      <c r="AW30" s="3">
+      <c r="AW30" s="7">
         <v>46.31</v>
       </c>
     </row>
     <row r="31" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K31" s="3">
+      <c r="K31" s="7">
         <v>544.09</v>
       </c>
-      <c r="AO31" s="3">
+      <c r="AO31" s="7">
         <v>59.55</v>
       </c>
-      <c r="AW31" s="3">
+      <c r="AW31" s="7">
         <v>47.56</v>
       </c>
     </row>
     <row r="32" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K32" s="3">
+      <c r="K32" s="7">
         <v>1558</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AO32" s="7">
         <v>93.05</v>
       </c>
-      <c r="AW32" s="3">
+      <c r="AW32" s="7">
         <v>47.56</v>
       </c>
     </row>
     <row r="33" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K33" s="3">
+      <c r="K33" s="7">
         <v>922.73</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AO33" s="7">
         <v>72.08</v>
       </c>
-      <c r="AW33" s="3">
+      <c r="AW33" s="7">
         <v>47.56</v>
       </c>
     </row>
     <row r="34" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K34" s="3">
+      <c r="K34" s="7">
         <v>1393.38</v>
       </c>
-      <c r="AO34" s="3">
+      <c r="AO34" s="7">
         <v>56.96</v>
       </c>
-      <c r="AW34" s="3">
+      <c r="AW34" s="7">
         <v>66.3</v>
       </c>
     </row>
     <row r="35" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K35" s="3">
+      <c r="K35" s="7">
         <v>468.6</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AO35" s="7">
         <v>88.99</v>
       </c>
-      <c r="AW35" s="3">
+      <c r="AW35" s="7">
         <v>48.43</v>
       </c>
     </row>
     <row r="36" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K36" s="3">
+      <c r="K36" s="7">
         <v>1322.42</v>
       </c>
-      <c r="AO36" s="3">
+      <c r="AO36" s="7">
         <v>92.42</v>
       </c>
-      <c r="AW36" s="3">
+      <c r="AW36" s="7">
         <v>61.54</v>
       </c>
     </row>
     <row r="37" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K37" s="3">
+      <c r="K37" s="7">
         <v>1502.64</v>
       </c>
-      <c r="AO37" s="3">
+      <c r="AO37" s="7">
         <v>65.16</v>
       </c>
-      <c r="AW37" s="3">
+      <c r="AW37" s="7">
         <v>48.43</v>
       </c>
     </row>
     <row r="38" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K38" s="3">
+      <c r="K38" s="7">
         <v>971.67</v>
       </c>
-      <c r="AO38" s="3">
+      <c r="AO38" s="7">
         <v>88.08</v>
       </c>
-      <c r="AW38" s="3">
+      <c r="AW38" s="7">
         <v>70.260000000000005</v>
       </c>
     </row>
     <row r="39" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K39" s="3">
+      <c r="K39" s="7">
         <v>1013.83</v>
       </c>
-      <c r="AW39" s="3">
+      <c r="AW39" s="7">
         <v>47.98</v>
       </c>
     </row>
     <row r="40" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K40" s="3">
+      <c r="K40" s="7">
         <v>1384.54</v>
       </c>
-      <c r="AW40" s="3">
+      <c r="AW40" s="7">
         <v>47.98</v>
       </c>
     </row>
     <row r="41" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K41" s="3">
+      <c r="K41" s="7">
         <v>534.64</v>
       </c>
-      <c r="AW41" s="3">
+      <c r="AW41" s="7">
         <v>63.42</v>
       </c>
     </row>
     <row r="42" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K42" s="3">
+      <c r="K42" s="7">
         <v>1488.29</v>
       </c>
-      <c r="AW42" s="3">
+      <c r="AW42" s="7">
         <v>66.3</v>
       </c>
     </row>
     <row r="43" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K43" s="3">
+      <c r="K43" s="7">
         <v>391.88</v>
       </c>
-      <c r="AW43" s="3">
+      <c r="AW43" s="7">
         <v>58.46</v>
       </c>
     </row>
     <row r="44" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K44" s="3">
+      <c r="K44" s="7">
         <v>1252.1500000000001</v>
       </c>
-      <c r="AW44" s="3">
+      <c r="AW44" s="7">
         <v>46.96</v>
       </c>
     </row>
     <row r="45" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K45" s="3">
+      <c r="K45" s="7">
         <v>898.96</v>
       </c>
-      <c r="AW45" s="3">
+      <c r="AW45" s="7">
         <v>60.34</v>
       </c>
     </row>
     <row r="46" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K46" s="3">
+      <c r="K46" s="7">
         <v>1225.8499999999999</v>
       </c>
-      <c r="AW46" s="3">
+      <c r="AW46" s="7">
         <v>46.96</v>
       </c>
     </row>
     <row r="47" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K47" s="3">
+      <c r="K47" s="7">
         <v>1314.72</v>
       </c>
-      <c r="AW47" s="3">
+      <c r="AW47" s="7">
         <v>74.290000000000006</v>
       </c>
     </row>
     <row r="48" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K48" s="3">
+      <c r="K48" s="7">
         <v>1337.95</v>
       </c>
-      <c r="AW48" s="3">
+      <c r="AW48" s="7">
         <v>61.27</v>
       </c>
     </row>
     <row r="49" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K49" s="3">
+      <c r="K49" s="7">
         <v>913.31</v>
       </c>
-      <c r="AW49" s="3">
+      <c r="AW49" s="7">
         <v>46.47</v>
       </c>
     </row>
     <row r="50" spans="11:49" x14ac:dyDescent="0.25">
-      <c r="K50" s="3">
+      <c r="K50" s="7">
         <v>460.19</v>
       </c>
-      <c r="AW50" s="3">
+      <c r="AW50" s="7">
         <v>46.47</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C25119E574720E44A3466601008EF346" ma:contentTypeVersion="17" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="7bc9fbd05695e6de40da560e90907c72">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="b1f2b182-2a7c-4659-bfd7-62191332dff4" xmlns:ns4="f2d4b666-1e6c-483d-90ce-71d6412817d8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f3a358de134b6d88c73532b09ef5a3f7" ns3:_="" ns4:_="">
+    <xsd:import namespace="b1f2b182-2a7c-4659-bfd7-62191332dff4"/>
+    <xsd:import namespace="f2d4b666-1e6c-483d-90ce-71d6412817d8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns4:SharingHintHash" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b1f2b182-2a7c-4659-bfd7-62191332dff4" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="16" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="18" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="19" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="20" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="21" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="22" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="24" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f2d4b666-1e6c-483d-90ce-71d6412817d8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="SharingHintHash" ma:index="14" nillable="true" ma:displayName="Hash de Dica de Compartilhamento" ma:hidden="true" ma:internalName="SharingHintHash" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="b1f2b182-2a7c-4659-bfd7-62191332dff4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E84F0A57-5C77-4617-B0BF-13FBAAE0064B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b1f2b182-2a7c-4659-bfd7-62191332dff4"/>
+    <ds:schemaRef ds:uri="f2d4b666-1e6c-483d-90ce-71d6412817d8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1416A96-8FCB-4E51-AFEE-F22E895A59B5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D293D5F-80D7-40DE-BF9A-C51290E5E00E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f2d4b666-1e6c-483d-90ce-71d6412817d8"/>
+    <ds:schemaRef ds:uri="b1f2b182-2a7c-4659-bfd7-62191332dff4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>